--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,135 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121702733</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57307</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO om Nyrud Hunneberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>348658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6467019</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Tunhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Orädd, sittande i död gran i svacka.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Larsson, Natalie Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>121702733</v>
       </c>
       <c r="B4" t="n">
-        <v>57307</v>
+        <v>57315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>121702733</v>
       </c>
       <c r="B4" t="n">
-        <v>57315</v>
+        <v>57319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>121702733</v>
       </c>
       <c r="B4" t="n">
-        <v>57319</v>
+        <v>57322</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>121702733</v>
       </c>
       <c r="B4" t="n">
-        <v>57322</v>
+        <v>57324</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128464368</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO om Nyrud Hunneberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>348658</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6467019</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Tunhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128464368</v>
       </c>
       <c r="B5" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128464368</v>
       </c>
       <c r="B5" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128464368</v>
       </c>
       <c r="B5" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128464368</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>128464368</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33755-2021 artfynd.xlsx
+++ b/artfynd/A 33755-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71435513</v>
+        <v>94768868</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyrud NO om, Vg</t>
+          <t>Nyrud, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348700.3908867151</v>
+        <v>348570</v>
       </c>
       <c r="R2" t="n">
-        <v>6466979.967289303</v>
+        <v>6466879</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Molinia kärr och barrskog</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +775,7 @@
         <v>94768883</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348515.6771033291</v>
+        <v>348515</v>
       </c>
       <c r="R3" t="n">
-        <v>6467135.871327599</v>
+        <v>6467135</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +840,9 @@
           <t>2021-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121702733</v>
+        <v>128464368</v>
       </c>
       <c r="B4" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -946,7 +906,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -986,27 +946,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Orädd, sittande i död gran i svacka.</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,17 +981,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Larsson, Natalie Johansson</t>
+          <t>Henrik Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128464368</v>
+        <v>121702733</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,16 +999,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,7 +1025,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1110,22 +1065,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2024-12-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:43</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Orädd, sittande i död gran i svacka.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1105,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henrik Larsson</t>
+          <t>Henrik Larsson, Natalie Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1269,6 +1229,210 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94768875</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nyrud, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>348700</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6466832</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Tunhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-07-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>71435513</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyrud NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>348700</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6466980</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vänersborg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Västra Tunhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-05-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Molinia kärr och barrskog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
